--- a/bin/Debug/Template/SparePartBalance.xlsx
+++ b/bin/Debug/Template/SparePartBalance.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\IT-Project\MC-Dept-App\bin\Debug\Template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3364CB3C-EB6D-4D5C-A6B9-F8E000685FE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F17C2EE-236D-485A-B341-2804C85C6423}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{5C9B76C0-C1B0-491E-AA96-3260EA1B797B}"/>
   </bookViews>
